--- a/Team-Data/2012-13/11-18-2012-13.xlsx
+++ b/Team-Data/2012-13/11-18-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,25 +806,25 @@
         <v>0.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AF2" t="n">
         <v>9</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AH2" t="n">
         <v>15</v>
       </c>
       <c r="AI2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK2" t="n">
         <v>8</v>
@@ -769,13 +836,13 @@
         <v>6</v>
       </c>
       <c r="AN2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO2" t="n">
         <v>28</v>
       </c>
       <c r="AP2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ2" t="n">
         <v>27</v>
@@ -784,16 +851,16 @@
         <v>24</v>
       </c>
       <c r="AS2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AT2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW2" t="n">
         <v>7</v>
@@ -805,7 +872,7 @@
         <v>3</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BA2" t="n">
         <v>19</v>
@@ -814,7 +881,7 @@
         <v>22</v>
       </c>
       <c r="BC2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>11-18-2012-13</t>
+          <t>2012-11-18</t>
         </is>
       </c>
     </row>
@@ -843,43 +910,43 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>0.545</v>
+        <v>0.6</v>
       </c>
       <c r="H3" t="n">
         <v>48.5</v>
       </c>
       <c r="I3" t="n">
-        <v>36.2</v>
+        <v>36.6</v>
       </c>
       <c r="J3" t="n">
-        <v>76.09999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.476</v>
+        <v>0.478</v>
       </c>
       <c r="L3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="M3" t="n">
-        <v>14.3</v>
+        <v>14</v>
       </c>
       <c r="N3" t="n">
-        <v>0.357</v>
+        <v>0.371</v>
       </c>
       <c r="O3" t="n">
-        <v>19.5</v>
+        <v>19.9</v>
       </c>
       <c r="P3" t="n">
-        <v>24.5</v>
+        <v>25</v>
       </c>
       <c r="Q3" t="n">
         <v>0.796</v>
@@ -888,115 +955,115 @@
         <v>6.8</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>30.7</v>
       </c>
       <c r="T3" t="n">
-        <v>36.8</v>
+        <v>37.5</v>
       </c>
       <c r="U3" t="n">
-        <v>24.1</v>
+        <v>25.3</v>
       </c>
       <c r="V3" t="n">
-        <v>13.8</v>
+        <v>13.4</v>
       </c>
       <c r="W3" t="n">
         <v>7.3</v>
       </c>
       <c r="X3" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="Z3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="AA3" t="n">
         <v>20</v>
       </c>
-      <c r="AA3" t="n">
-        <v>20.2</v>
-      </c>
       <c r="AB3" t="n">
-        <v>96.90000000000001</v>
+        <v>98.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1.2</v>
+        <v>0.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AG3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AH3" t="n">
         <v>12</v>
       </c>
       <c r="AI3" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AJ3" t="n">
         <v>29</v>
       </c>
       <c r="AK3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM3" t="n">
         <v>28</v>
       </c>
       <c r="AN3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AO3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AP3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR3" t="n">
         <v>30</v>
       </c>
       <c r="AS3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AT3" t="n">
         <v>30</v>
       </c>
       <c r="AU3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AW3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AX3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BB3" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BC3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>11-18-2012-13</t>
+          <t>2012-11-18</t>
         </is>
       </c>
     </row>
@@ -1025,64 +1092,64 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>0.75</v>
+        <v>0.714</v>
       </c>
       <c r="H4" t="n">
         <v>48</v>
       </c>
       <c r="I4" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="J4" t="n">
-        <v>78.90000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.453</v>
+        <v>0.45</v>
       </c>
       <c r="L4" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="M4" t="n">
-        <v>20.9</v>
+        <v>21.4</v>
       </c>
       <c r="N4" t="n">
-        <v>0.335</v>
+        <v>0.34</v>
       </c>
       <c r="O4" t="n">
-        <v>19</v>
+        <v>18.6</v>
       </c>
       <c r="P4" t="n">
-        <v>25.8</v>
+        <v>25.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.738</v>
+        <v>0.718</v>
       </c>
       <c r="R4" t="n">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="S4" t="n">
-        <v>29.8</v>
+        <v>30.3</v>
       </c>
       <c r="T4" t="n">
-        <v>41.5</v>
+        <v>42.7</v>
       </c>
       <c r="U4" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="V4" t="n">
-        <v>13.9</v>
+        <v>14.4</v>
       </c>
       <c r="W4" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="X4" t="n">
         <v>5.9</v>
@@ -1091,79 +1158,79 @@
         <v>4.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="AB4" t="n">
-        <v>97.5</v>
+        <v>97.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AE4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF4" t="n">
         <v>3</v>
       </c>
       <c r="AG4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AH4" t="n">
         <v>15</v>
       </c>
       <c r="AI4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AJ4" t="n">
         <v>23</v>
       </c>
       <c r="AK4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AM4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AP4" t="n">
         <v>4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AR4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AS4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AT4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AU4" t="n">
         <v>22</v>
       </c>
       <c r="AV4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AW4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY4" t="n">
         <v>5</v>
@@ -1175,10 +1242,10 @@
         <v>3</v>
       </c>
       <c r="BB4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>11-18-2012-13</t>
+          <t>2012-11-18</t>
         </is>
       </c>
     </row>
@@ -1285,16 +1352,16 @@
         <v>-3.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AF5" t="n">
         <v>9</v>
       </c>
       <c r="AG5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AH5" t="n">
         <v>9</v>
@@ -1309,7 +1376,7 @@
         <v>25</v>
       </c>
       <c r="AL5" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AM5" t="n">
         <v>23</v>
@@ -1318,16 +1385,16 @@
         <v>30</v>
       </c>
       <c r="AO5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ5" t="n">
         <v>13</v>
       </c>
       <c r="AR5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS5" t="n">
         <v>23</v>
@@ -1345,19 +1412,19 @@
         <v>7</v>
       </c>
       <c r="AX5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY5" t="n">
         <v>29</v>
       </c>
       <c r="AZ5" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB5" t="n">
         <v>20</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>19</v>
       </c>
       <c r="BC5" t="n">
         <v>23</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>11-18-2012-13</t>
+          <t>2012-11-18</t>
         </is>
       </c>
     </row>
@@ -1389,94 +1456,94 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
         <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5</v>
+        <v>0.556</v>
       </c>
       <c r="H6" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I6" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J6" t="n">
-        <v>81</v>
+        <v>81.7</v>
       </c>
       <c r="K6" t="n">
-        <v>0.444</v>
+        <v>0.439</v>
       </c>
       <c r="L6" t="n">
         <v>3.7</v>
       </c>
       <c r="M6" t="n">
-        <v>12.1</v>
+        <v>11.7</v>
       </c>
       <c r="N6" t="n">
-        <v>0.306</v>
+        <v>0.314</v>
       </c>
       <c r="O6" t="n">
-        <v>19.1</v>
+        <v>19.4</v>
       </c>
       <c r="P6" t="n">
-        <v>24.2</v>
+        <v>24.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.789</v>
+        <v>0.781</v>
       </c>
       <c r="R6" t="n">
-        <v>11.9</v>
+        <v>12.6</v>
       </c>
       <c r="S6" t="n">
-        <v>30.6</v>
+        <v>30.8</v>
       </c>
       <c r="T6" t="n">
-        <v>42.5</v>
+        <v>43.3</v>
       </c>
       <c r="U6" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="V6" t="n">
-        <v>15.5</v>
+        <v>15.1</v>
       </c>
       <c r="W6" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="X6" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="AB6" t="n">
-        <v>94.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="AD6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF6" t="n">
         <v>9</v>
       </c>
-      <c r="AE6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>13</v>
-      </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AH6" t="n">
         <v>11</v>
@@ -1485,10 +1552,10 @@
         <v>18</v>
       </c>
       <c r="AJ6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL6" t="n">
         <v>30</v>
@@ -1497,52 +1564,52 @@
         <v>30</v>
       </c>
       <c r="AN6" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AO6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ6" t="n">
         <v>7</v>
       </c>
-      <c r="AP6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>5</v>
-      </c>
       <c r="AR6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AS6" t="n">
         <v>14</v>
       </c>
       <c r="AT6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AU6" t="n">
         <v>4</v>
       </c>
       <c r="AV6" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AW6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AX6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY6" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AZ6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB6" t="n">
         <v>21</v>
       </c>
       <c r="BC6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>11-18-2012-13</t>
+          <t>2012-11-18</t>
         </is>
       </c>
     </row>
@@ -1571,142 +1638,142 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2</v>
+        <v>0.222</v>
       </c>
       <c r="H7" t="n">
         <v>48</v>
       </c>
       <c r="I7" t="n">
-        <v>35.8</v>
+        <v>36.4</v>
       </c>
       <c r="J7" t="n">
-        <v>84.59999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0.423</v>
+        <v>0.43</v>
       </c>
       <c r="L7" t="n">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="M7" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="N7" t="n">
-        <v>0.355</v>
+        <v>0.365</v>
       </c>
       <c r="O7" t="n">
-        <v>16.3</v>
+        <v>16.6</v>
       </c>
       <c r="P7" t="n">
-        <v>23.2</v>
+        <v>24.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.703</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>13.3</v>
+        <v>12.8</v>
       </c>
       <c r="S7" t="n">
-        <v>27.4</v>
+        <v>27.1</v>
       </c>
       <c r="T7" t="n">
-        <v>40.7</v>
+        <v>39.9</v>
       </c>
       <c r="U7" t="n">
-        <v>19.7</v>
+        <v>20.3</v>
       </c>
       <c r="V7" t="n">
         <v>16.4</v>
       </c>
       <c r="W7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="X7" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="Y7" t="n">
         <v>8.9</v>
       </c>
       <c r="Z7" t="n">
-        <v>21.2</v>
+        <v>21.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>20.2</v>
+        <v>20.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>95.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC7" t="n">
         <v>-7</v>
       </c>
       <c r="AD7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AG7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH7" t="n">
         <v>15</v>
       </c>
       <c r="AI7" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AJ7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM7" t="n">
         <v>5</v>
       </c>
       <c r="AN7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AO7" t="n">
         <v>19</v>
       </c>
       <c r="AP7" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AQ7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AR7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AS7" t="n">
         <v>30</v>
       </c>
       <c r="AT7" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AU7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AV7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AX7" t="n">
         <v>30</v>
@@ -1715,13 +1782,13 @@
         <v>30</v>
       </c>
       <c r="AZ7" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BA7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BB7" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BC7" t="n">
         <v>28</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>11-18-2012-13</t>
+          <t>2012-11-18</t>
         </is>
       </c>
     </row>
@@ -1834,16 +1901,16 @@
         <v>1</v>
       </c>
       <c r="AE8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH8" t="n">
         <v>13</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>12</v>
       </c>
       <c r="AI8" t="n">
         <v>9</v>
@@ -1855,46 +1922,46 @@
         <v>7</v>
       </c>
       <c r="AL8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR8" t="n">
         <v>26</v>
       </c>
       <c r="AS8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX8" t="n">
         <v>15</v>
       </c>
-      <c r="AU8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>14</v>
-      </c>
       <c r="AY8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ8" t="n">
         <v>26</v>
@@ -1906,7 +1973,7 @@
         <v>6</v>
       </c>
       <c r="BC8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>11-18-2012-13</t>
+          <t>2012-11-18</t>
         </is>
       </c>
     </row>
@@ -2013,19 +2080,19 @@
         <v>-2.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AF9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AG9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AI9" t="n">
         <v>1</v>
@@ -2034,7 +2101,7 @@
         <v>2</v>
       </c>
       <c r="AK9" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AL9" t="n">
         <v>18</v>
@@ -2043,10 +2110,10 @@
         <v>12</v>
       </c>
       <c r="AN9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO9" t="n">
         <v>27</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>25</v>
       </c>
       <c r="AP9" t="n">
         <v>20</v>
@@ -2058,19 +2125,19 @@
         <v>1</v>
       </c>
       <c r="AS9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT9" t="n">
         <v>1</v>
       </c>
       <c r="AU9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AV9" t="n">
         <v>25</v>
       </c>
       <c r="AW9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX9" t="n">
         <v>7</v>
@@ -2079,13 +2146,13 @@
         <v>27</v>
       </c>
       <c r="AZ9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA9" t="n">
         <v>22</v>
       </c>
       <c r="BB9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC9" t="n">
         <v>20</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>11-18-2012-13</t>
+          <t>2012-11-18</t>
         </is>
       </c>
     </row>
@@ -2117,88 +2184,88 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>9</v>
       </c>
       <c r="G10" t="n">
-        <v>0.182</v>
+        <v>0.1</v>
       </c>
       <c r="H10" t="n">
         <v>48</v>
       </c>
       <c r="I10" t="n">
-        <v>35.5</v>
+        <v>35.1</v>
       </c>
       <c r="J10" t="n">
-        <v>79.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.445</v>
+        <v>0.437</v>
       </c>
       <c r="L10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="M10" t="n">
-        <v>14.4</v>
+        <v>14.7</v>
       </c>
       <c r="N10" t="n">
         <v>0.354</v>
       </c>
       <c r="O10" t="n">
-        <v>17.9</v>
+        <v>17.6</v>
       </c>
       <c r="P10" t="n">
-        <v>24.2</v>
+        <v>24</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.741</v>
+        <v>0.733</v>
       </c>
       <c r="R10" t="n">
-        <v>10.5</v>
+        <v>10.9</v>
       </c>
       <c r="S10" t="n">
-        <v>28.3</v>
+        <v>27.9</v>
       </c>
       <c r="T10" t="n">
         <v>38.8</v>
       </c>
       <c r="U10" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="V10" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="W10" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="X10" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="AA10" t="n">
         <v>20.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>93.90000000000001</v>
+        <v>93</v>
       </c>
       <c r="AC10" t="n">
-        <v>-4.4</v>
+        <v>-6.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE10" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AF10" t="n">
         <v>30</v>
@@ -2213,31 +2280,31 @@
         <v>24</v>
       </c>
       <c r="AJ10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK10" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AL10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM10" t="n">
         <v>27</v>
       </c>
       <c r="AN10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO10" t="n">
         <v>15</v>
       </c>
       <c r="AP10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AQ10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AR10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS10" t="n">
         <v>29</v>
@@ -2246,31 +2313,31 @@
         <v>28</v>
       </c>
       <c r="AU10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AV10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW10" t="n">
         <v>27</v>
       </c>
       <c r="AX10" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AY10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>11-18-2012-13</t>
+          <t>2012-11-18</t>
         </is>
       </c>
     </row>
@@ -2299,148 +2366,148 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
         <v>5</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5</v>
+        <v>0.556</v>
       </c>
       <c r="H11" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="I11" t="n">
-        <v>37</v>
+        <v>36.3</v>
       </c>
       <c r="J11" t="n">
-        <v>83.2</v>
+        <v>83.3</v>
       </c>
       <c r="K11" t="n">
-        <v>0.445</v>
+        <v>0.436</v>
       </c>
       <c r="L11" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="M11" t="n">
-        <v>19.1</v>
+        <v>19.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0.304</v>
+        <v>0.303</v>
       </c>
       <c r="O11" t="n">
         <v>18</v>
       </c>
       <c r="P11" t="n">
-        <v>24.6</v>
+        <v>24.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.732</v>
+        <v>0.723</v>
       </c>
       <c r="R11" t="n">
-        <v>11.7</v>
+        <v>12.1</v>
       </c>
       <c r="S11" t="n">
-        <v>32.8</v>
+        <v>33.4</v>
       </c>
       <c r="T11" t="n">
-        <v>44.5</v>
+        <v>45.6</v>
       </c>
       <c r="U11" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="V11" t="n">
-        <v>16.6</v>
+        <v>17</v>
       </c>
       <c r="W11" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X11" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>23.4</v>
+        <v>24</v>
       </c>
       <c r="AA11" t="n">
-        <v>21.9</v>
+        <v>22.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>97.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>-2.4</v>
+        <v>-1.6</v>
       </c>
       <c r="AD11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF11" t="n">
         <v>9</v>
       </c>
-      <c r="AE11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>13</v>
-      </c>
       <c r="AG11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AH11" t="n">
         <v>3</v>
       </c>
       <c r="AI11" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AJ11" t="n">
         <v>13</v>
       </c>
       <c r="AK11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AM11" t="n">
         <v>13</v>
       </c>
-      <c r="AL11" t="n">
-        <v>22</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>14</v>
-      </c>
       <c r="AN11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO11" t="n">
         <v>14</v>
       </c>
       <c r="AP11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AT11" t="n">
         <v>6</v>
       </c>
       <c r="AU11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AW11" t="n">
         <v>23</v>
       </c>
       <c r="AX11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AY11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ11" t="n">
         <v>27</v>
@@ -2449,10 +2516,10 @@
         <v>5</v>
       </c>
       <c r="BB11" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="BC11" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>11-18-2012-13</t>
+          <t>2012-11-18</t>
         </is>
       </c>
     </row>
@@ -2481,106 +2548,106 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
         <v>4</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4</v>
+        <v>0.444</v>
       </c>
       <c r="H12" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="I12" t="n">
-        <v>36.3</v>
+        <v>35.4</v>
       </c>
       <c r="J12" t="n">
-        <v>84.5</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.43</v>
+        <v>0.423</v>
       </c>
       <c r="L12" t="n">
         <v>8.9</v>
       </c>
       <c r="M12" t="n">
-        <v>28</v>
+        <v>28.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0.318</v>
+        <v>0.311</v>
       </c>
       <c r="O12" t="n">
-        <v>18.7</v>
+        <v>19.6</v>
       </c>
       <c r="P12" t="n">
-        <v>23.8</v>
+        <v>24.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.786</v>
+        <v>0.8</v>
       </c>
       <c r="R12" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="S12" t="n">
-        <v>32.6</v>
+        <v>32.8</v>
       </c>
       <c r="T12" t="n">
-        <v>45.4</v>
+        <v>45.8</v>
       </c>
       <c r="U12" t="n">
-        <v>22.5</v>
+        <v>21.7</v>
       </c>
       <c r="V12" t="n">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="W12" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="AA12" t="n">
-        <v>18.6</v>
+        <v>19</v>
       </c>
       <c r="AB12" t="n">
-        <v>100.2</v>
+        <v>99.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.6</v>
+        <v>0.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG12" t="n">
         <v>18</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>20</v>
       </c>
       <c r="AH12" t="n">
         <v>3</v>
       </c>
       <c r="AI12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AJ12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AK12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL12" t="n">
         <v>3</v>
@@ -2589,43 +2656,43 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AP12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AQ12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS12" t="n">
         <v>6</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>7</v>
       </c>
       <c r="AT12" t="n">
         <v>5</v>
       </c>
       <c r="AU12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AV12" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AW12" t="n">
         <v>11</v>
       </c>
       <c r="AX12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AY12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA12" t="n">
         <v>26</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>11-18-2012-13</t>
+          <t>2012-11-18</t>
         </is>
       </c>
     </row>
@@ -2663,115 +2730,115 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
         <v>4</v>
       </c>
       <c r="F13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G13" t="n">
-        <v>0.364</v>
+        <v>0.4</v>
       </c>
       <c r="H13" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="I13" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="J13" t="n">
-        <v>81.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.405</v>
+        <v>0.406</v>
       </c>
       <c r="L13" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="M13" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="N13" t="n">
-        <v>0.314</v>
+        <v>0.305</v>
       </c>
       <c r="O13" t="n">
-        <v>16.1</v>
+        <v>16.5</v>
       </c>
       <c r="P13" t="n">
-        <v>22.5</v>
+        <v>22.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.717</v>
+        <v>0.721</v>
       </c>
       <c r="R13" t="n">
-        <v>13.3</v>
+        <v>13.7</v>
       </c>
       <c r="S13" t="n">
-        <v>35.3</v>
+        <v>35</v>
       </c>
       <c r="T13" t="n">
-        <v>48.5</v>
+        <v>48.7</v>
       </c>
       <c r="U13" t="n">
-        <v>17.9</v>
+        <v>17.6</v>
       </c>
       <c r="V13" t="n">
-        <v>16.5</v>
+        <v>16.3</v>
       </c>
       <c r="W13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="X13" t="n">
         <v>6.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="Z13" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>19.8</v>
+        <v>20.3</v>
       </c>
       <c r="AB13" t="n">
-        <v>88.09999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AD13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE13" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AF13" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG13" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AH13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI13" t="n">
         <v>30</v>
       </c>
       <c r="AJ13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK13" t="n">
         <v>29</v>
       </c>
       <c r="AL13" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AM13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN13" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AO13" t="n">
         <v>20</v>
@@ -2780,10 +2847,10 @@
         <v>18</v>
       </c>
       <c r="AQ13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS13" t="n">
         <v>1</v>
@@ -2792,31 +2859,31 @@
         <v>2</v>
       </c>
       <c r="AU13" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AV13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW13" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AX13" t="n">
         <v>8</v>
       </c>
       <c r="AY13" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AZ13" t="n">
         <v>1</v>
       </c>
       <c r="BA13" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="BB13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BC13" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>11-18-2012-13</t>
+          <t>2012-11-18</t>
         </is>
       </c>
     </row>
@@ -2923,10 +2990,10 @@
         <v>9.300000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AE14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF14" t="n">
         <v>3</v>
@@ -2953,31 +3020,31 @@
         <v>19</v>
       </c>
       <c r="AN14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AO14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP14" t="n">
         <v>5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR14" t="n">
         <v>27</v>
       </c>
       <c r="AS14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV14" t="n">
         <v>26</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>28</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -2986,10 +3053,10 @@
         <v>5</v>
       </c>
       <c r="AY14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ14" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA14" t="n">
         <v>9</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>11-18-2012-13</t>
+          <t>2012-11-18</t>
         </is>
       </c>
     </row>
@@ -3027,127 +3094,127 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
         <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5</v>
+        <v>0.444</v>
       </c>
       <c r="H15" t="n">
         <v>48</v>
       </c>
       <c r="I15" t="n">
-        <v>36.4</v>
+        <v>35.3</v>
       </c>
       <c r="J15" t="n">
-        <v>78.7</v>
+        <v>78</v>
       </c>
       <c r="K15" t="n">
-        <v>0.463</v>
+        <v>0.453</v>
       </c>
       <c r="L15" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="M15" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="N15" t="n">
-        <v>0.345</v>
+        <v>0.333</v>
       </c>
       <c r="O15" t="n">
-        <v>20.6</v>
+        <v>20.9</v>
       </c>
       <c r="P15" t="n">
-        <v>29.9</v>
+        <v>30.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.694</v>
       </c>
       <c r="R15" t="n">
-        <v>14.1</v>
+        <v>14.7</v>
       </c>
       <c r="S15" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="T15" t="n">
-        <v>46.8</v>
+        <v>47.4</v>
       </c>
       <c r="U15" t="n">
-        <v>21.3</v>
+        <v>20.7</v>
       </c>
       <c r="V15" t="n">
-        <v>16.9</v>
+        <v>17.3</v>
       </c>
       <c r="W15" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="X15" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>17.8</v>
+        <v>18.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>100.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE15" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AF15" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AG15" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AH15" t="n">
         <v>15</v>
       </c>
       <c r="AI15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL15" t="n">
         <v>14</v>
       </c>
-      <c r="AJ15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>13</v>
-      </c>
       <c r="AM15" t="n">
         <v>10</v>
       </c>
       <c r="AN15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AO15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP15" t="n">
         <v>1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AR15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS15" t="n">
         <v>6</v>
@@ -3156,31 +3223,31 @@
         <v>3</v>
       </c>
       <c r="AU15" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AV15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AW15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AX15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY15" t="n">
         <v>12</v>
       </c>
-      <c r="AY15" t="n">
-        <v>11</v>
-      </c>
       <c r="AZ15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA15" t="n">
         <v>1</v>
       </c>
       <c r="BB15" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="BC15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>11-18-2012-13</t>
+          <t>2012-11-18</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>9</v>
       </c>
       <c r="AD16" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3308,19 +3375,19 @@
         <v>6</v>
       </c>
       <c r="AK16" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AL16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM16" t="n">
         <v>26</v>
       </c>
       <c r="AN16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AO16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP16" t="n">
         <v>6</v>
@@ -3332,31 +3399,31 @@
         <v>8</v>
       </c>
       <c r="AS16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU16" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AV16" t="n">
         <v>4</v>
       </c>
       <c r="AW16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BA16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BB16" t="n">
         <v>4</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>11-18-2012-13</t>
+          <t>2012-11-18</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3545,7 @@
         <v>7</v>
       </c>
       <c r="AG17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH17" t="n">
         <v>15</v>
@@ -3487,7 +3554,7 @@
         <v>3</v>
       </c>
       <c r="AJ17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK17" t="n">
         <v>2</v>
@@ -3499,7 +3566,7 @@
         <v>7</v>
       </c>
       <c r="AN17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO17" t="n">
         <v>18</v>
@@ -3508,13 +3575,13 @@
         <v>19</v>
       </c>
       <c r="AQ17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR17" t="n">
         <v>28</v>
       </c>
       <c r="AS17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AT17" t="n">
         <v>29</v>
@@ -3523,19 +3590,19 @@
         <v>5</v>
       </c>
       <c r="AV17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY17" t="n">
         <v>4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA17" t="n">
         <v>18</v>
@@ -3544,7 +3611,7 @@
         <v>1</v>
       </c>
       <c r="BC17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>11-18-2012-13</t>
+          <t>2012-11-18</t>
         </is>
       </c>
     </row>
@@ -3651,10 +3718,10 @@
         <v>3.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF18" t="n">
         <v>3</v>
@@ -3678,10 +3745,10 @@
         <v>15</v>
       </c>
       <c r="AM18" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AN18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO18" t="n">
         <v>22</v>
@@ -3699,16 +3766,16 @@
         <v>10</v>
       </c>
       <c r="AT18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AU18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV18" t="n">
         <v>11</v>
       </c>
       <c r="AW18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AX18" t="n">
         <v>9</v>
@@ -3720,7 +3787,7 @@
         <v>14</v>
       </c>
       <c r="BA18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB18" t="n">
         <v>5</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>11-18-2012-13</t>
+          <t>2012-11-18</t>
         </is>
       </c>
     </row>
@@ -3833,10 +3900,10 @@
         <v>1.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AE19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AF19" t="n">
         <v>9</v>
@@ -3866,16 +3933,16 @@
         <v>29</v>
       </c>
       <c r="AO19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP19" t="n">
         <v>2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR19" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AS19" t="n">
         <v>12</v>
@@ -3890,16 +3957,16 @@
         <v>21</v>
       </c>
       <c r="AW19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX19" t="n">
         <v>1</v>
       </c>
       <c r="AY19" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA19" t="n">
         <v>2</v>
@@ -3908,7 +3975,7 @@
         <v>25</v>
       </c>
       <c r="BC19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>11-18-2012-13</t>
+          <t>2012-11-18</t>
         </is>
       </c>
     </row>
@@ -4015,16 +4082,16 @@
         <v>-3.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE20" t="n">
         <v>24</v>
       </c>
       <c r="AF20" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AG20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH20" t="n">
         <v>15</v>
@@ -4033,10 +4100,10 @@
         <v>26</v>
       </c>
       <c r="AJ20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK20" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AL20" t="n">
         <v>17</v>
@@ -4057,10 +4124,10 @@
         <v>3</v>
       </c>
       <c r="AR20" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AS20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT20" t="n">
         <v>19</v>
@@ -4069,25 +4136,25 @@
         <v>8</v>
       </c>
       <c r="AV20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA20" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB20" t="n">
         <v>23</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>24</v>
       </c>
       <c r="BC20" t="n">
         <v>22</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>11-18-2012-13</t>
+          <t>2012-11-18</t>
         </is>
       </c>
     </row>
@@ -4119,61 +4186,61 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>0.875</v>
+        <v>0.857</v>
       </c>
       <c r="H21" t="n">
         <v>48</v>
       </c>
       <c r="I21" t="n">
-        <v>37.4</v>
+        <v>38</v>
       </c>
       <c r="J21" t="n">
-        <v>82.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.452</v>
+        <v>0.466</v>
       </c>
       <c r="L21" t="n">
-        <v>10.4</v>
+        <v>10.9</v>
       </c>
       <c r="M21" t="n">
-        <v>26.4</v>
+        <v>26.6</v>
       </c>
       <c r="N21" t="n">
-        <v>0.393</v>
+        <v>0.409</v>
       </c>
       <c r="O21" t="n">
         <v>15.4</v>
       </c>
       <c r="P21" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.75</v>
+        <v>0.745</v>
       </c>
       <c r="R21" t="n">
-        <v>10.3</v>
+        <v>9.6</v>
       </c>
       <c r="S21" t="n">
-        <v>29.9</v>
+        <v>29.4</v>
       </c>
       <c r="T21" t="n">
-        <v>40.1</v>
+        <v>39</v>
       </c>
       <c r="U21" t="n">
         <v>19.4</v>
       </c>
       <c r="V21" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="W21" t="n">
         <v>9.300000000000001</v>
@@ -4182,25 +4249,25 @@
         <v>3.9</v>
       </c>
       <c r="Y21" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>18</v>
+        <v>18.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>100.5</v>
+        <v>102.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AE21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF21" t="n">
         <v>1</v>
@@ -4212,13 +4279,13 @@
         <v>15</v>
       </c>
       <c r="AI21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ21" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AK21" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4227,7 +4294,7 @@
         <v>2</v>
       </c>
       <c r="AN21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO21" t="n">
         <v>24</v>
@@ -4236,40 +4303,40 @@
         <v>25</v>
       </c>
       <c r="AQ21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR21" t="n">
         <v>23</v>
       </c>
       <c r="AS21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AT21" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AU21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX21" t="n">
         <v>26</v>
       </c>
       <c r="AY21" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA21" t="n">
         <v>23</v>
       </c>
       <c r="BB21" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BC21" t="n">
         <v>1</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>11-18-2012-13</t>
+          <t>2012-11-18</t>
         </is>
       </c>
     </row>
@@ -4301,100 +4368,100 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F22" t="n">
         <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>0.727</v>
+        <v>0.7</v>
       </c>
       <c r="H22" t="n">
         <v>48</v>
       </c>
       <c r="I22" t="n">
-        <v>35.8</v>
+        <v>35.2</v>
       </c>
       <c r="J22" t="n">
-        <v>74.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.482</v>
+        <v>0.48</v>
       </c>
       <c r="L22" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="M22" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="N22" t="n">
-        <v>0.435</v>
+        <v>0.41</v>
       </c>
       <c r="O22" t="n">
         <v>22.5</v>
       </c>
       <c r="P22" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="Q22" t="n">
         <v>0.84</v>
       </c>
       <c r="R22" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="S22" t="n">
-        <v>33.2</v>
+        <v>33.5</v>
       </c>
       <c r="T22" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="U22" t="n">
-        <v>22.4</v>
+        <v>21.5</v>
       </c>
       <c r="V22" t="n">
-        <v>16.8</v>
+        <v>17.3</v>
       </c>
       <c r="W22" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="X22" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.9</v>
+        <v>21.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>21.5</v>
+        <v>21.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>101.7</v>
+        <v>100</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AF22" t="n">
         <v>7</v>
       </c>
       <c r="AG22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH22" t="n">
         <v>15</v>
       </c>
       <c r="AI22" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AJ22" t="n">
         <v>30</v>
@@ -4403,13 +4470,13 @@
         <v>3</v>
       </c>
       <c r="AL22" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AM22" t="n">
         <v>24</v>
       </c>
       <c r="AN22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO22" t="n">
         <v>1</v>
@@ -4421,7 +4488,7 @@
         <v>1</v>
       </c>
       <c r="AR22" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS22" t="n">
         <v>2</v>
@@ -4430,28 +4497,28 @@
         <v>18</v>
       </c>
       <c r="AU22" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AV22" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AW22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AY22" t="n">
         <v>1</v>
       </c>
       <c r="AZ22" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BA22" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB22" t="n">
         <v>8</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>3</v>
       </c>
       <c r="BC22" t="n">
         <v>4</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>11-18-2012-13</t>
+          <t>2012-11-18</t>
         </is>
       </c>
     </row>
@@ -4483,115 +4550,115 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
         <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G23" t="n">
-        <v>0.333</v>
+        <v>0.375</v>
       </c>
       <c r="H23" t="n">
         <v>48</v>
       </c>
       <c r="I23" t="n">
-        <v>36</v>
+        <v>36.5</v>
       </c>
       <c r="J23" t="n">
-        <v>82.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="K23" t="n">
-        <v>0.437</v>
+        <v>0.441</v>
       </c>
       <c r="L23" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="M23" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="N23" t="n">
-        <v>0.368</v>
+        <v>0.375</v>
       </c>
       <c r="O23" t="n">
-        <v>13.1</v>
+        <v>12.5</v>
       </c>
       <c r="P23" t="n">
-        <v>17.2</v>
+        <v>16.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.761</v>
+        <v>0.746</v>
       </c>
       <c r="R23" t="n">
-        <v>10.7</v>
+        <v>11</v>
       </c>
       <c r="S23" t="n">
         <v>31.4</v>
       </c>
       <c r="T23" t="n">
-        <v>42.1</v>
+        <v>42.4</v>
       </c>
       <c r="U23" t="n">
-        <v>22.7</v>
+        <v>23.3</v>
       </c>
       <c r="V23" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W23" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="X23" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="Y23" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="Z23" t="n">
-        <v>19.7</v>
+        <v>19.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>16.3</v>
+        <v>15.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>90.2</v>
+        <v>90.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.7</v>
+        <v>-5</v>
       </c>
       <c r="AD23" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AE23" t="n">
         <v>24</v>
       </c>
       <c r="AF23" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AG23" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AH23" t="n">
         <v>15</v>
       </c>
       <c r="AI23" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AJ23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK23" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AL23" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AM23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AN23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO23" t="n">
         <v>29</v>
@@ -4600,10 +4667,10 @@
         <v>29</v>
       </c>
       <c r="AQ23" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AR23" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AS23" t="n">
         <v>11</v>
@@ -4612,7 +4679,7 @@
         <v>14</v>
       </c>
       <c r="AU23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV23" t="n">
         <v>17</v>
@@ -4621,13 +4688,13 @@
         <v>30</v>
       </c>
       <c r="AX23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY23" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AZ23" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
@@ -4636,7 +4703,7 @@
         <v>27</v>
       </c>
       <c r="BC23" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>11-18-2012-13</t>
+          <t>2012-11-18</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F24" t="n">
         <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6</v>
+        <v>0.556</v>
       </c>
       <c r="H24" t="n">
         <v>48</v>
@@ -4683,76 +4750,76 @@
         <v>33.8</v>
       </c>
       <c r="J24" t="n">
-        <v>82.5</v>
+        <v>82.8</v>
       </c>
       <c r="K24" t="n">
-        <v>0.41</v>
+        <v>0.408</v>
       </c>
       <c r="L24" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="M24" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="N24" t="n">
-        <v>0.387</v>
+        <v>0.38</v>
       </c>
       <c r="O24" t="n">
-        <v>13.9</v>
+        <v>14.4</v>
       </c>
       <c r="P24" t="n">
-        <v>18</v>
+        <v>18.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.772</v>
+        <v>0.774</v>
       </c>
       <c r="R24" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="S24" t="n">
         <v>31.8</v>
       </c>
       <c r="T24" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="U24" t="n">
-        <v>20.2</v>
+        <v>19.4</v>
       </c>
       <c r="V24" t="n">
-        <v>13.5</v>
+        <v>13.7</v>
       </c>
       <c r="W24" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X24" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="Z24" t="n">
-        <v>17.7</v>
+        <v>18</v>
       </c>
       <c r="AA24" t="n">
-        <v>17.6</v>
+        <v>17.8</v>
       </c>
       <c r="AB24" t="n">
-        <v>88.90000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>-1.2</v>
+        <v>-2.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF24" t="n">
         <v>9</v>
       </c>
       <c r="AG24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH24" t="n">
         <v>15</v>
@@ -4761,7 +4828,7 @@
         <v>27</v>
       </c>
       <c r="AJ24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK24" t="n">
         <v>28</v>
@@ -4770,16 +4837,16 @@
         <v>12</v>
       </c>
       <c r="AM24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ24" t="n">
         <v>10</v>
@@ -4791,34 +4858,34 @@
         <v>9</v>
       </c>
       <c r="AT24" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AU24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW24" t="n">
         <v>13</v>
       </c>
       <c r="AX24" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY24" t="n">
         <v>15</v>
       </c>
       <c r="AZ24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA24" t="n">
         <v>27</v>
       </c>
       <c r="BB24" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC24" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>11-18-2012-13</t>
+          <t>2012-11-18</t>
         </is>
       </c>
     </row>
@@ -4928,16 +4995,16 @@
         <v>1</v>
       </c>
       <c r="AE25" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AF25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG25" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AH25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI25" t="n">
         <v>4</v>
@@ -4973,13 +5040,13 @@
         <v>25</v>
       </c>
       <c r="AT25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW25" t="n">
         <v>12</v>
@@ -4988,19 +5055,19 @@
         <v>6</v>
       </c>
       <c r="AY25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>11-18-2012-13</t>
+          <t>2012-11-18</t>
         </is>
       </c>
     </row>
@@ -5029,94 +5096,94 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F26" t="n">
         <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5</v>
+        <v>0.444</v>
       </c>
       <c r="H26" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="I26" t="n">
-        <v>37.1</v>
+        <v>36.9</v>
       </c>
       <c r="J26" t="n">
-        <v>84.2</v>
+        <v>84.8</v>
       </c>
       <c r="K26" t="n">
-        <v>0.441</v>
+        <v>0.435</v>
       </c>
       <c r="L26" t="n">
         <v>8.9</v>
       </c>
       <c r="M26" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="O26" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="P26" t="n">
         <v>23.1</v>
       </c>
-      <c r="N26" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="O26" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="P26" t="n">
-        <v>22.8</v>
-      </c>
       <c r="Q26" t="n">
-        <v>0.759</v>
+        <v>0.76</v>
       </c>
       <c r="R26" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="S26" t="n">
-        <v>28.3</v>
+        <v>28.8</v>
       </c>
       <c r="T26" t="n">
-        <v>40.5</v>
+        <v>41.2</v>
       </c>
       <c r="U26" t="n">
-        <v>19</v>
+        <v>19.4</v>
       </c>
       <c r="V26" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W26" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="X26" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z26" t="n">
-        <v>19.9</v>
+        <v>20.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>100.4</v>
+        <v>100.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>-1.4</v>
+        <v>-2.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE26" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AF26" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AG26" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AH26" t="n">
         <v>3</v>
@@ -5125,10 +5192,10 @@
         <v>10</v>
       </c>
       <c r="AJ26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AK26" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AL26" t="n">
         <v>3</v>
@@ -5137,7 +5204,7 @@
         <v>4</v>
       </c>
       <c r="AN26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO26" t="n">
         <v>16</v>
@@ -5146,19 +5213,19 @@
         <v>17</v>
       </c>
       <c r="AQ26" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AR26" t="n">
         <v>11</v>
       </c>
       <c r="AS26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AU26" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AV26" t="n">
         <v>12</v>
@@ -5167,22 +5234,22 @@
         <v>10</v>
       </c>
       <c r="AX26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ26" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BA26" t="n">
         <v>7</v>
       </c>
       <c r="BB26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BC26" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>11-18-2012-13</t>
+          <t>2012-11-18</t>
         </is>
       </c>
     </row>
@@ -5211,94 +5278,94 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E27" t="n">
         <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2</v>
+        <v>0.222</v>
       </c>
       <c r="H27" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="I27" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J27" t="n">
-        <v>86.09999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="K27" t="n">
-        <v>0.418</v>
+        <v>0.414</v>
       </c>
       <c r="L27" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="M27" t="n">
         <v>17.8</v>
       </c>
       <c r="N27" t="n">
-        <v>0.298</v>
+        <v>0.294</v>
       </c>
       <c r="O27" t="n">
-        <v>13.9</v>
+        <v>14.3</v>
       </c>
       <c r="P27" t="n">
         <v>19.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.728</v>
+        <v>0.75</v>
       </c>
       <c r="R27" t="n">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="S27" t="n">
-        <v>28.3</v>
+        <v>28.4</v>
       </c>
       <c r="T27" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="U27" t="n">
-        <v>17.3</v>
+        <v>17.8</v>
       </c>
       <c r="V27" t="n">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="W27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="X27" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y27" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="Z27" t="n">
         <v>24.3</v>
       </c>
       <c r="AA27" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>91.2</v>
+        <v>91.3</v>
       </c>
       <c r="AC27" t="n">
         <v>-8.800000000000001</v>
       </c>
       <c r="AD27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF27" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AG27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH27" t="n">
         <v>3</v>
@@ -5310,10 +5377,10 @@
         <v>3</v>
       </c>
       <c r="AK27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM27" t="n">
         <v>22</v>
@@ -5328,31 +5395,31 @@
         <v>26</v>
       </c>
       <c r="AQ27" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AR27" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AS27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AV27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AW27" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AX27" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AY27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>11-18-2012-13</t>
+          <t>2012-11-18</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>5.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5489,10 +5556,10 @@
         <v>5</v>
       </c>
       <c r="AJ28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL28" t="n">
         <v>8</v>
@@ -5510,7 +5577,7 @@
         <v>22</v>
       </c>
       <c r="AQ28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR28" t="n">
         <v>25</v>
@@ -5519,10 +5586,10 @@
         <v>13</v>
       </c>
       <c r="AT28" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AU28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV28" t="n">
         <v>15</v>
@@ -5531,19 +5598,19 @@
         <v>9</v>
       </c>
       <c r="AX28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA28" t="n">
         <v>25</v>
       </c>
       <c r="BB28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BC28" t="n">
         <v>5</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>11-18-2012-13</t>
+          <t>2012-11-18</t>
         </is>
       </c>
     </row>
@@ -5575,91 +5642,91 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
         <v>7</v>
       </c>
       <c r="G29" t="n">
-        <v>0.3</v>
+        <v>0.222</v>
       </c>
       <c r="H29" t="n">
-        <v>49.5</v>
+        <v>49.7</v>
       </c>
       <c r="I29" t="n">
-        <v>35.1</v>
+        <v>34.8</v>
       </c>
       <c r="J29" t="n">
-        <v>83.7</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>0.419</v>
+        <v>0.413</v>
       </c>
       <c r="L29" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="M29" t="n">
-        <v>21</v>
+        <v>21.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0.362</v>
+        <v>0.359</v>
       </c>
       <c r="O29" t="n">
-        <v>18.3</v>
+        <v>18.8</v>
       </c>
       <c r="P29" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.775</v>
+        <v>0.793</v>
       </c>
       <c r="R29" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="S29" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="T29" t="n">
         <v>40</v>
       </c>
       <c r="U29" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="V29" t="n">
-        <v>13.2</v>
+        <v>13.6</v>
       </c>
       <c r="W29" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X29" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="Y29" t="n">
-        <v>6.3</v>
+        <v>6.9</v>
       </c>
       <c r="Z29" t="n">
-        <v>24.4</v>
+        <v>24.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>96.09999999999999</v>
+        <v>96</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3.7</v>
+        <v>-5.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE29" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AF29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG29" t="n">
         <v>26</v>
@@ -5671,64 +5738,64 @@
         <v>25</v>
       </c>
       <c r="AJ29" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AK29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AM29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN29" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AO29" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AP29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ29" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AR29" t="n">
         <v>17</v>
       </c>
       <c r="AS29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT29" t="n">
+        <v>22</v>
+      </c>
+      <c r="AU29" t="n">
         <v>24</v>
       </c>
-      <c r="AU29" t="n">
-        <v>23</v>
-      </c>
       <c r="AV29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW29" t="n">
         <v>13</v>
       </c>
       <c r="AX29" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AY29" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BB29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>11-18-2012-13</t>
+          <t>2012-11-18</t>
         </is>
       </c>
     </row>
@@ -5838,25 +5905,25 @@
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AF30" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AG30" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AH30" t="n">
         <v>2</v>
       </c>
       <c r="AI30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ30" t="n">
         <v>9</v>
       </c>
       <c r="AK30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL30" t="n">
         <v>19</v>
@@ -5865,16 +5932,16 @@
         <v>21</v>
       </c>
       <c r="AN30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO30" t="n">
         <v>13</v>
       </c>
       <c r="AP30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR30" t="n">
         <v>4</v>
@@ -5886,31 +5953,31 @@
         <v>4</v>
       </c>
       <c r="AU30" t="n">
+        <v>19</v>
+      </c>
+      <c r="AV30" t="n">
         <v>20</v>
       </c>
-      <c r="AV30" t="n">
-        <v>19</v>
-      </c>
       <c r="AW30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY30" t="n">
         <v>20</v>
       </c>
       <c r="AZ30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB30" t="n">
         <v>15</v>
       </c>
       <c r="BC30" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>11-18-2012-13</t>
+          <t>2012-11-18</t>
         </is>
       </c>
     </row>
@@ -6017,13 +6084,13 @@
         <v>-7.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE31" t="n">
         <v>30</v>
       </c>
       <c r="AF31" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AG31" t="n">
         <v>30</v>
@@ -6035,7 +6102,7 @@
         <v>28</v>
       </c>
       <c r="AJ31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK31" t="n">
         <v>30</v>
@@ -6056,16 +6123,16 @@
         <v>30</v>
       </c>
       <c r="AQ31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR31" t="n">
         <v>16</v>
       </c>
       <c r="AS31" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AT31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU31" t="n">
         <v>9</v>
@@ -6077,13 +6144,13 @@
         <v>15</v>
       </c>
       <c r="AX31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA31" t="n">
         <v>29</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>11-18-2012-13</t>
+          <t>2012-11-18</t>
         </is>
       </c>
     </row>
